--- a/19/4.1 ML Projects/2.Projects/Final_Regression_01/Data_Train_Test/y_test_true.xlsx
+++ b/19/4.1 ML Projects/2.Projects/Final_Regression_01/Data_Train_Test/y_test_true.xlsx
@@ -425,205 +425,133 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Salary</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="B2" t="n">
+      <c r="A2" t="n">
         <v>93400</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>47</v>
-      </c>
-      <c r="B3" t="n">
+      <c r="A3" t="n">
         <v>126400</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B4" t="n">
+      <c r="A4" t="n">
         <v>90100</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>55</v>
-      </c>
-      <c r="B5" t="n">
+      <c r="A5" t="n">
         <v>182800</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B6" t="n">
+      <c r="A6" t="n">
         <v>93200</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>64</v>
-      </c>
-      <c r="B7" t="n">
+      <c r="A7" t="n">
         <v>96800</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>73</v>
-      </c>
-      <c r="B8" t="n">
+      <c r="A8" t="n">
         <v>163400</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B9" t="n">
+      <c r="A9" t="n">
         <v>71300</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="B10" t="n">
+      <c r="A10" t="n">
         <v>94100</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>107</v>
-      </c>
-      <c r="B11" t="n">
+      <c r="A11" t="n">
         <v>600000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B12" t="n">
+      <c r="A12" t="n">
         <v>117100</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>62</v>
-      </c>
-      <c r="B13" t="n">
+      <c r="A13" t="n">
         <v>161000</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" t="n">
+      <c r="A14" t="n">
         <v>212200</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="B15" t="n">
+      <c r="A15" t="n">
         <v>101600</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>89</v>
-      </c>
-      <c r="B16" t="n">
+      <c r="A16" t="n">
         <v>112600</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>91</v>
-      </c>
-      <c r="B17" t="n">
+      <c r="A17" t="n">
         <v>163900</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>109</v>
-      </c>
-      <c r="B18" t="n">
+      <c r="A18" t="n">
         <v>350000</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B19" t="n">
+      <c r="A19" t="n">
         <v>119300</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>88</v>
-      </c>
-      <c r="B20" t="n">
+      <c r="A20" t="n">
         <v>184500</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>104</v>
-      </c>
-      <c r="B21" t="n">
+      <c r="A21" t="n">
         <v>520000</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>65</v>
-      </c>
-      <c r="B22" t="n">
+      <c r="A22" t="n">
         <v>121100</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>45</v>
-      </c>
-      <c r="B23" t="n">
+      <c r="A23" t="n">
         <v>115100</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="B24" t="n">
+      <c r="A24" t="n">
         <v>92900</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>70</v>
-      </c>
-      <c r="B25" t="n">
+      <c r="A25" t="n">
         <v>153200</v>
       </c>
     </row>
